--- a/assets/templates/KML_larvae_template.xlsx
+++ b/assets/templates/KML_larvae_template.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="유충" sheetId="1" r:id="R41d9976d41a24859"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시" sheetId="2" r:id="R0ba6ccd07e074880"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="3" r:id="R437e5ce0f55e435c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="유충" sheetId="1" r:id="R070ccab88c12452f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시" sheetId="2" r:id="Rfdba1616bb6a4a68"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="3" r:id="R9adbd312b08246af"/>
   </x:sheets>
 </x:workbook>
 </file>
